--- a/example/demo_database/database_options.xlsx
+++ b/example/demo_database/database_options.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="signals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="loops" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="spectrograms" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="psds" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="signals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="loops" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spectrograms" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="psds" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1228,16 +1228,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
@@ -2607,6 +2597,266 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2423</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HR (ICCA 2423)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>bpm</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>crimson</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SpO2 (ICCA 2630)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>steelblue</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>19602</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ABP mean (ICCA 19602)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ICCA blood pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NIBP systolic (ICCA 6041)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ICCA blood pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>6043</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NIBP diastolic (ICCA 6043)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ICCA blood pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>6048</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NIBP mean (ICCA 6048)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>ICCA blood pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>4347</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PEEP (ICCA 4347)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>seagreen</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ICCA airway pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>17324</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Peak Pressure (ICCA 17324)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ICCA airway pressures</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>icca</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>17728</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plateau Pressure (ICCA 17728)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ICCA airway pressures</t>
         </is>
       </c>
     </row>

--- a/example/demo_database/database_options.xlsx
+++ b/example/demo_database/database_options.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,8 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13.33203125" customWidth="1" min="17" max="17"/>
     <col width="13.33203125" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,6 +541,16 @@
           <t>opacity</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -604,29 +616,60 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pleth</t>
+          <t>art_lp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plethysmography</t>
+          <t>Arterial pressure, low-pass 0.5 Hz</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Arterial Pressure</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>art</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>lowpass(cutoff_hz=0.5)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>other::numerics</t>
+          <t>other::waves</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>pleth</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Plethysmography</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU</t>
         </is>
       </c>
     </row>
@@ -638,22 +681,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Heart Rate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>bpm</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Arterial Pressure</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -665,21 +693,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNId</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pressure diastolic</t>
+          <t>Heart Rate</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1.5</v>
+          <t>bpm</t>
+        </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -695,25 +720,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNIm</t>
+          <t>FC_ma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pressure mean</t>
+          <t>Heart Rate, 1-min average</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1.5</v>
+          <t>bpm</t>
+        </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>Arterial Pressure</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>moving_average(window_s=60)</t>
         </is>
       </c>
     </row>
@@ -725,12 +757,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNIs</t>
+          <t>PNId</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pressure systolic</t>
+          <t>Pressure diastolic</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -750,44 +782,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>other::syringe</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>lines+markers</t>
+          <t>PNIm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pressure mean</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Arterial Pressure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>other::syringe</t>
+          <t>other::numerics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vitesse Babynoradrenaline</t>
+          <t>PNIs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pressure systolic</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>µg/h</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Arterial Pressure</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eit</t>
+          <t>other::syringe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -795,46 +850,30 @@
           <t>*</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Asia/Karachi</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>0.7</v>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>lines+markers</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eit</t>
+          <t>other::syringe</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Vitesse Babynoradrenaline</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ohms</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>EIT Impedance</t>
-        </is>
+          <t>µg/h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -845,23 +884,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Local 1*</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Ohms</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>EIT Impedance</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Asia/Karachi</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="15">
@@ -872,7 +910,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Local 2*</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -882,7 +920,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>black</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -899,7 +937,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Local 3*</t>
+          <t>Local 1*</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -909,7 +947,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -926,7 +964,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Local 4*</t>
+          <t>Local 2*</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -936,7 +974,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -953,27 +991,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>%Local 1*</t>
+          <t>Local 3*</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Proportion</t>
+          <t>Ohms</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>green</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>EIT Impedance</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>fraction</t>
         </is>
       </c>
     </row>
@@ -985,27 +1018,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>%Local 2*</t>
+          <t>Local 4*</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Proportion</t>
+          <t>Ohms</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>EIT Impedance</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>percentage</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1045,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>%Local 3*</t>
+          <t>%Local 1*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1027,12 +1055,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>EIT Impedance</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>fraction</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1077,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>%Local 4*</t>
+          <t>%Local 2*</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1054,67 +1087,71 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>EIT Impedance</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>percentage</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>servo_u</t>
+          <t>eit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>UTC</t>
+          <t>%Local 3*</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Proportion</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>EIT Impedance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>servo_u</t>
+          <t>eit</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Airway Press. (cmH2O)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Airway Pressure</t>
+          <t>%Local 4*</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>Proportion</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>#e74c3c</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Pressure &amp; Flow</t>
+          <t>EIT Impedance</t>
         </is>
       </c>
     </row>
@@ -1126,33 +1163,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Volume (ml)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G24" t="n">
-        <v>800</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>#3498db</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Volume</t>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1164,25 +1186,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Airway Flow (ml / s)</t>
+          <t>Airway Press. (cmH2O)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Airway Flow</t>
+          <t>Airway Pressure</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>L/min</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>0.06</v>
+          <t>cmH2O</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>#2ecc71</t>
+          <t>#e74c3c</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1199,37 +1218,108 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Volume (ml)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G26" t="n">
+        <v>800</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>#3498db</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>servo_u</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Airway Flow (ml / s)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Airway Flow</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>L/min</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#2ecc71</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Pressure &amp; Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>servo_u</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Esophageal Press. (cmH2O)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Esophageal Pressure</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>cmH2O</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>#e74c3c</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>dash</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Esophageal Pressure</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
@@ -1238,56 +1328,8 @@
     <row r="34"/>
     <row r="35"/>
     <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>mindray_scope</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>mindray_scope</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ECG_II</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ECG II</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>#2c3e50</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Waveform</t>
-        </is>
-      </c>
-    </row>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -1296,28 +1338,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pleth</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Plethysmography</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>#7d3c98</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Waveform</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
@@ -1328,28 +1356,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Art</t>
+          <t>ECG_II</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Arterial Pressure</t>
+          <t>ECG II</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>200</v>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#2c3e50</t>
+        </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Arterial Pressure</t>
+          <t>Waveform</t>
         </is>
       </c>
     </row>
@@ -1361,27 +1388,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Paw</t>
+          <t>Pleth</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Airway Pressure</t>
+          <t>Plethysmography</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>#e67e22</t>
+          <t>#7d3c98</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Pressure &amp; Flow</t>
+          <t>Waveform</t>
         </is>
       </c>
     </row>
@@ -1393,27 +1420,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vol</t>
+          <t>Art</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Arterial Pressure</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>#2471a3</t>
-        </is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>200</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Arterial Pressure</t>
         </is>
       </c>
     </row>
@@ -1425,22 +1453,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>debit</t>
+          <t>Paw</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Airway Pressure</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>L/min</t>
+          <t>cmH2O</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>#1e8449</t>
+          <t>#e67e22</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -1457,81 +1485,91 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>Vol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Port 4 Pressure</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>#2471a3</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Esophageal Pressure</t>
+          <t>Volume</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>edf</t>
+          <t>mindray_scope</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>chan 1</t>
+          <t>debit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EEG 1</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>µV</t>
+          <t>L/min</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>steelblue</t>
+          <t>#1e8449</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Pressure &amp; Flow</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>edf</t>
+          <t>mindray_scope</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>chan 2</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EEG 2</t>
+          <t>Port 4 Pressure</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>µV</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>darkorange</t>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Esophageal Pressure</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1581,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>chan 3</t>
+          <t>chan 1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EEG 3</t>
+          <t>EEG 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1558,63 +1596,61 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>seagreen</t>
+          <t>steelblue</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fluxmed_signals</t>
+          <t>edf</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.02</v>
+          <t>chan 2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>EEG 2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>µV</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>darkorange</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fluxmed_signals</t>
+          <t>edf</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Paw(cmH2O)</t>
+          <t>chan 3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Airway Pressure (Fluxmed)</t>
+          <t>EEG 3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>40</v>
+          <t>µV</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Fluxmed waveforms</t>
+          <t>seagreen</t>
         </is>
       </c>
     </row>
@@ -1626,34 +1662,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Volume(ml)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Volume (Fluxmed)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G50" t="n">
-        <v>800</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>steelblue</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Fluxmed waveforms</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="51">
@@ -1664,22 +1680,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Flow(l/min)</t>
+          <t>Paw(cmH2O)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Flow (Fluxmed)</t>
+          <t>Airway Pressure (Fluxmed)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>L/min</t>
-        </is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>40</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>darkgreen</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -1696,32 +1718,33 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pes(cmH2O)</t>
+          <t>Volume(ml)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Esophageal Pressure (Fluxmed)</t>
+          <t>Volume (Fluxmed)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
+          <t>mL</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G52" t="n">
+        <v>800</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>dot</t>
+          <t>steelblue</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Fluxmed esophageal</t>
+          <t>Fluxmed waveforms</t>
         </is>
       </c>
     </row>
@@ -1733,27 +1756,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ptpulm(cmH2O)</t>
+          <t>Flow(l/min)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Transpulmonary Pressure (Fluxmed)</t>
+          <t>Flow (Fluxmed)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>L/min</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>darkgreen</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Fluxmed esophageal</t>
+          <t>Fluxmed waveforms</t>
         </is>
       </c>
     </row>
@@ -1765,70 +1788,93 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CO2(mmHg)</t>
+          <t>Pes(cmH2O)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CO2 (Fluxmed)</t>
+          <t>Esophageal Pressure (Fluxmed)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>50</v>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Fluxmed esophageal</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fluxmed_parameters</t>
+          <t>fluxmed_signals</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
+          <t>Ptpulm(cmH2O)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Transpulmonary Pressure (Fluxmed)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Fluxmed esophageal</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fluxmed_parameters</t>
+          <t>fluxmed_signals</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RR(bpm)</t>
+          <t>CO2(mmHg)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Respiratory Rate (Fluxmed)</t>
+          <t>CO2 (Fluxmed)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>/min</t>
+          <t>mmHg</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
@@ -1839,23 +1885,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VT(ml)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tidal Volume (Fluxmed)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Fluxmed breath volumes</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -1866,23 +1903,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MV(l)</t>
+          <t>RR(bpm)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minute Volume (Fluxmed)</t>
+          <t>Respiratory Rate (Fluxmed)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>L/min</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Fluxmed breath volumes</t>
-        </is>
+          <t>/min</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -1893,27 +1931,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEEP(cmH2O)</t>
+          <t>VT(ml)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PEEP (Fluxmed)</t>
+          <t>Tidal Volume (Fluxmed)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>steelblue</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Fluxmed breath pressures</t>
+          <t>Fluxmed breath volumes</t>
         </is>
       </c>
     </row>
@@ -1925,27 +1958,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pplat(cmH2O)</t>
+          <t>MV(l)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plateau Pressure (Fluxmed)</t>
+          <t>Minute Volume (Fluxmed)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>dash</t>
+          <t>L/min</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Fluxmed breath pressures</t>
+          <t>Fluxmed breath volumes</t>
         </is>
       </c>
     </row>
@@ -1957,17 +1985,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PIP(cmH2O)</t>
+          <t>PEEP(cmH2O)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Peak Pressure (Fluxmed)</t>
+          <t>PEEP (Fluxmed)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>steelblue</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -1984,12 +2017,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DrivingPaw(cmH2O)</t>
+          <t>Pplat(cmH2O)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Driving Pressure (Fluxmed)</t>
+          <t>Plateau Pressure (Fluxmed)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1997,9 +2030,14 @@
           <t>cmH2O</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>dash</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Fluxmed mechanics</t>
+          <t>Fluxmed breath pressures</t>
         </is>
       </c>
     </row>
@@ -2011,22 +2049,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cstat(ml/cmH2O)</t>
+          <t>PIP(cmH2O)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Static Compliance (Fluxmed)</t>
+          <t>Peak Pressure (Fluxmed)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>mL/cmH2O</t>
+          <t>cmH2O</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Fluxmed mechanics</t>
+          <t>Fluxmed breath pressures</t>
         </is>
       </c>
     </row>
@@ -2038,17 +2076,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PesSwing(cmH2O)</t>
+          <t>DrivingPaw(cmH2O)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Esophageal Swing (Fluxmed)</t>
+          <t>Driving Pressure (Fluxmed)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Fluxmed mechanics</t>
         </is>
       </c>
     </row>
@@ -2060,80 +2103,73 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EtCO2(mmHg)</t>
+          <t>Cstat(ml/cmH2O)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EtCO2 (Fluxmed)</t>
+          <t>Static Compliance (Fluxmed)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>20</v>
-      </c>
-      <c r="G65" t="n">
-        <v>60</v>
+          <t>mL/cmH2O</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Fluxmed mechanics</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>mindray_respi_waves</t>
+          <t>fluxmed_parameters</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0.02</v>
+          <t>PesSwing(cmH2O)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Esophageal Swing (Fluxmed)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>mindray_respi_waves</t>
+          <t>fluxmed_parameters</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MDC_PRESS_AWAY-MDC_DIM_CM_H2O</t>
+          <t>EtCO2(mmHg)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Paw (Mindray respi)</t>
+          <t>EtCO2 (Fluxmed)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>mmHg</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="G67" t="n">
-        <v>40</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Mindray respi waveforms</t>
-        </is>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
@@ -2144,34 +2180,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MDC_VOL_AWAY-MDC_DIM_MILLI_L</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Volume (Mindray respi)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G68" t="n">
-        <v>600</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>steelblue</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Mindray respi waveforms</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="69">
@@ -2182,28 +2198,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MDC_FLOW_AWAY-MDC_DIM_L_PER_MIN</t>
+          <t>MDC_PRESS_AWAY-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Flow (Mindray respi)</t>
+          <t>Paw (Mindray respi)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>L/min</t>
+          <t>cmH2O</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>-100</v>
+        <v>-5</v>
       </c>
       <c r="G69" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>darkgreen</t>
+          <t>red</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -2220,38 +2236,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MDC_PRESS_ESOPH-MDC_DIM_CM_H2O</t>
+          <t>MDC_VOL_AWAY-MDC_DIM_MILLI_L</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poes (Mindray respi)</t>
+          <t>Volume (Mindray respi)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>-20</v>
+        <v>-50</v>
       </c>
       <c r="G70" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>dot</t>
+          <t>steelblue</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Mindray respi esophageal</t>
+          <t>Mindray respi waveforms</t>
         </is>
       </c>
     </row>
@@ -2263,33 +2274,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MDC_PRESS_TRANSPULM-MDC_DIM_CM_H2O</t>
+          <t>MDC_FLOW_AWAY-MDC_DIM_L_PER_MIN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ptranspulm (Mindray respi)</t>
+          <t>Flow (Mindray respi)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>cmH2O</t>
+          <t>L/min</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="G71" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>darkgreen</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Mindray respi esophageal</t>
+          <t>Mindray respi waveforms</t>
         </is>
       </c>
     </row>
@@ -2301,69 +2312,105 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MDC_CONC_AWAY_CO2-MDC_DIM_MMHG</t>
+          <t>MDC_PRESS_ESOPH-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CO2 (Mindray respi)</t>
+          <t>Poes (Mindray respi)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>mmHg</t>
+          <t>cmH2O</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>20</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Mindray respi esophageal</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mindray_respi_numerics</t>
+          <t>mindray_respi_waves</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
+          <t>MDC_PRESS_TRANSPULM-MDC_DIM_CM_H2O</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ptranspulm (Mindray respi)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G73" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Mindray respi esophageal</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>mindray_respi_numerics</t>
+          <t>mindray_respi_waves</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MDC_VOL_AWAY_TIDAL_EXP-MDC_DIM_MILLI_L</t>
+          <t>MDC_CONC_AWAY_CO2-MDC_DIM_MMHG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tidal Volume exp (Mindray respi)</t>
+          <t>CO2 (Mindray respi)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>mL</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Mindray respi breath volumes</t>
-        </is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="75">
@@ -2374,23 +2421,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MDC_VENT_VOL_MINUTE_EXP-MDC_DIM_L_PER_MIN</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Minute Volume exp (Mindray respi)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>L/min</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Mindray respi breath volumes</t>
-        </is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -2401,27 +2439,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MDC_VENT_PRESS_AWAY_END_EXP_POS-MDC_DIM_CM_H2O</t>
+          <t>MDC_VOL_AWAY_TIDAL_EXP-MDC_DIM_MILLI_L</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PEEP (Mindray respi)</t>
+          <t>Tidal Volume exp (Mindray respi)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>steelblue</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Mindray respi breath pressures</t>
+          <t>Mindray respi breath volumes</t>
         </is>
       </c>
     </row>
@@ -2433,27 +2466,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MDC_PRESS_RESP_PLAT-MDC_DIM_CM_H2O</t>
+          <t>MDC_VENT_VOL_MINUTE_EXP-MDC_DIM_L_PER_MIN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Plateau Pressure (Mindray respi)</t>
+          <t>Minute Volume exp (Mindray respi)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cmH2O</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>dash</t>
+          <t>L/min</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Mindray respi breath pressures</t>
+          <t>Mindray respi breath volumes</t>
         </is>
       </c>
     </row>
@@ -2465,17 +2493,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MDC_PRESS_AWAY_MAX-MDC_DIM_CM_H2O</t>
+          <t>MDC_VENT_PRESS_AWAY_END_EXP_POS-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Peak Pressure (Mindray respi)</t>
+          <t>PEEP (Mindray respi)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>steelblue</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -2492,22 +2525,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MDC_COMPL_LUNG-MDC_DIM_MILLI_L_PER_CM_H2O</t>
+          <t>MDC_PRESS_RESP_PLAT-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lung Compliance (Mindray respi)</t>
+          <t>Plateau Pressure (Mindray respi)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>mL/cmH2O</t>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>dash</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Mindray respi mechanics</t>
+          <t>Mindray respi breath pressures</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2557,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MNDRY_VENT_PDRIVE-MDC_DIM_CM_H2O</t>
+          <t>MDC_PRESS_AWAY_MAX-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Driving Pressure (Mindray respi)</t>
+          <t>Peak Pressure (Mindray respi)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2534,7 +2572,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Mindray respi mechanics</t>
+          <t>Mindray respi breath pressures</t>
         </is>
       </c>
     </row>
@@ -2546,17 +2584,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MNDRY_VENT_MPRS-MNDRY_DIM_JOULES_PER_MIN</t>
+          <t>MDC_COMPL_LUNG-MDC_DIM_MILLI_L_PER_CM_H2O</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mechanical Power (Mindray respi)</t>
+          <t>Lung Compliance (Mindray respi)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>J/min</t>
+          <t>mL/cmH2O</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Mindray respi mechanics</t>
         </is>
       </c>
     </row>
@@ -2568,43 +2611,92 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MDC_CONC_AWAY_CO2_ET-MDC_DIM_MMHG</t>
+          <t>MNDRY_VENT_PDRIVE-MDC_DIM_CM_H2O</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EtCO2 (Mindray respi)</t>
+          <t>Driving Pressure (Mindray respi)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>mmHg</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>20</v>
-      </c>
-      <c r="G82" t="n">
-        <v>60</v>
+          <t>cmH2O</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Mindray respi mechanics</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>mindray_respi_numerics</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MNDRY_VENT_MPRS-MNDRY_DIM_JOULES_PER_MIN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Mechanical Power (Mindray respi)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>J/min</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>mindray_respi_numerics</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MDC_CONC_AWAY_CO2_ET-MDC_DIM_MMHG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EtCO2 (Mindray respi)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>20</v>
+      </c>
+      <c r="G84" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>fluxmed_parameters</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Comments(-)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Operator comments (text)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
